--- a/parameters_simulation (version 1).xlsb.xlsx
+++ b/parameters_simulation (version 1).xlsb.xlsx
@@ -5,19 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rehan\meine_repos\Masterarbeit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rehan\meine_Repos\Masterarbeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EA8A5A4-6F2F-4DFF-807D-BF86D2673F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3C84F2-D4D6-4872-AA43-E03ACCB99D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" activeTab="1" xr2:uid="{A9158FE8-4C15-45A2-AFBE-76AC3C37AE55}"/>
+    <workbookView xWindow="38280" yWindow="3000" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A9158FE8-4C15-45A2-AFBE-76AC3C37AE55}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
     <sheet name="Tabelle1 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>cens_rate</t>
   </si>
@@ -99,6 +98,119 @@
   <si>
     <t>tau = 37
 params_data_creation = { 'shape_weibull': 1, 'scale_weibull_base': 24_300, 'rate_censoring': 0.003,
+                        'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
+                        'n': n, 'seed': seed, 'tau': tau}</t>
+  </si>
+  <si>
+    <t>tau = 37
+params_data_creation = { 'shape_weibull': 1, 
+                        'scale_weibull_base':  12463.811039838654   , 
+                        'rate_censoring': 0.010725364504143705      ,
+                        'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
+                        'n': n, 'seed': seed, 'tau': tau}</t>
+  </si>
+  <si>
+    <t>tau = 37
+params_data_creation = { 'shape_weibull': 1, 
+                        'scale_weibull_base':  5122.0241237382925    , 
+                        'rate_censoring':  0.012470507897824007      ,
+                        'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
+                        'n': n, 'seed': seed, 'tau': tau}</t>
+  </si>
+  <si>
+    <t>tau = 37
+params_data_creation = { 'shape_weibull': 1, 
+                        'scale_weibull_base':7500     , 
+                        'rate_censoring':  0.011600103696876245    ,
+                        'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
+                        'n': n, 'seed': seed, 'tau': tau}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+tau = 37
+params_data_creation = { 'shape_weibull': 1, 
+                        'scale_weibull_base':   28000   , 
+                        'rate_censoring': 0.01,
+                        'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
+                        'n': n, 'seed': seed, 'tau': tau}</t>
+  </si>
+  <si>
+    <t>tau = 37
+params_data_creation = { 'shape_weibull': 1, 
+                        'scale_weibull_base':  4453.164150258696    , 
+                        'rate_censoring': 0.003624326851330594   ,
+                        'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
+                        'n': n, 'seed': seed, 'tau': tau}</t>
+  </si>
+  <si>
+    <t>tau = 37
+params_data_creation = { 'shape_weibull': 1, 
+                        'scale_weibull_base': 6539.41883092019  , 
+                        'rate_censoring':0.0033904243453215187,
+                        'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
+                        'n': n, 'seed': seed, 'tau': tau}</t>
+  </si>
+  <si>
+    <t>tau = 37
+params_data_creation = { 'shape_weibull': 1, 
+                        'scale_weibull_base': 10803.76159628643   , 
+                        'rate_censoring':0.003170578469623819    ,
+                        'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
+                        'n': n, 'seed': seed, 'tau': tau}</t>
+  </si>
+  <si>
+    <t>tau = 37
+params_data_creation = { 'shape_weibull': 1, 
+                        'scale_weibull_base': 15800      , 
+                        'rate_censoring':  0.02052170406791234   ,
+                        'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
+                        'n': n, 'seed': seed, 'tau': tau}</t>
+  </si>
+  <si>
+    <t>tau = 37
+params_data_creation = { 'shape_weibull': 1, 
+                        'scale_weibull_base': 34000     , 
+                        'rate_censoring':  0.019578490533008537    ,
+                        'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
+                        'n': n, 'seed': seed, 'tau': tau}</t>
+  </si>
+  <si>
+    <t>tau = 37
+params_data_creation = { 'shape_weibull': 1, 
+                        'scale_weibull_base': 9600      , 
+                        'rate_censoring':  0.0218      ,
+                        'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
+                        'n': n, 'seed': seed, 'tau': tau}</t>
+  </si>
+  <si>
+    <t>tau = 37
+params_data_creation = { 'shape_weibull': 1, 
+                        'scale_weibull_base': 6600       , 
+                        'rate_censoring':  00.022901136686777616      ,
+                        'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
+                        'n': n, 'seed': seed, 'tau': tau}</t>
+  </si>
+  <si>
+    <t>tau = 37
+params_data_creation = { 'shape_weibull': 1, 
+                        'scale_weibull_base': 45_000       , 
+                        'rate_censoring':  0.034   ,
+                        'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
+                        'n': n, 'seed': seed, 'tau': tau}</t>
+  </si>
+  <si>
+    <t>tau = 37
+params_data_creation = { 'shape_weibull': 1, 
+                        'scale_weibull_base': 21700       , 
+                        'rate_censoring':  0.0352   ,
+                        'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
+                        'n': n, 'seed': seed, 'tau': tau}</t>
+  </si>
+  <si>
+    <t>tau = 37
+params_data_creation = { 'shape_weibull': 1, 
+                        'scale_weibull_base': 13_000       , 
+                        'rate_censoring':  0.0375   ,
                         'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
                         'n': n, 'seed': seed, 'tau': tau}</t>
   </si>
@@ -126,12 +238,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="12">
@@ -276,7 +394,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -303,9 +421,26 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
@@ -642,12 +777,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36E41AC1-747E-41BC-92B4-340E1417BCFD}">
   <dimension ref="C3:F20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="91" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>0</v>
       </c>
@@ -655,13 +790,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="3:6" ht="27.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="3:6" ht="27.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F4">
         <f>1-C5/100</f>
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="3:6" ht="79.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="3:6" ht="79.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C5" s="9">
         <v>10</v>
       </c>
@@ -676,7 +811,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="6" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="3:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C6" s="3"/>
       <c r="D6" s="9">
         <v>30</v>
@@ -689,7 +824,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="7" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="3:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C7" s="3"/>
       <c r="D7" s="7">
         <v>50</v>
@@ -702,7 +837,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="8" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="3:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C8" s="5"/>
       <c r="D8" s="9">
         <v>70</v>
@@ -715,13 +850,13 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="9" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F9" s="15">
         <f>(100-C10)/100</f>
         <v>0.7</v>
       </c>
     </row>
-    <row r="10" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="3:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C10" s="11">
         <v>30</v>
       </c>
@@ -736,7 +871,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="11" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="3:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C11" s="3"/>
       <c r="D11" s="7">
         <v>30</v>
@@ -749,7 +884,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="12" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="3:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C12" s="3"/>
       <c r="D12" s="9">
         <v>50</v>
@@ -762,7 +897,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="13" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C13" s="5"/>
       <c r="D13" s="8">
         <v>70</v>
@@ -773,7 +908,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="15" spans="3:6" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:6" ht="72" x14ac:dyDescent="0.3">
       <c r="C15">
         <v>50</v>
       </c>
@@ -784,15 +919,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="3:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D16">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E17" s="1"/>
     </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C20">
         <v>70</v>
       </c>
@@ -808,13 +943,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{159EE627-6F7C-4466-B497-718A4C378B66}">
-  <dimension ref="C3:F26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="C3:H26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="91" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>0</v>
       </c>
@@ -822,247 +957,343 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="3:6" ht="27.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="3:8" ht="27.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F4">
         <f>1-C5/100</f>
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="3:6" ht="79.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C5" s="9">
+    <row r="5" spans="3:8" ht="79.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="16">
         <v>10</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="17">
         <v>10</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="19">
         <f>$F$4*D5/100</f>
         <v>0.09</v>
       </c>
-    </row>
-    <row r="6" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C6" s="3"/>
-      <c r="D6" s="9">
+      <c r="G5">
+        <v>8.99</v>
+      </c>
+      <c r="H5">
+        <v>10.01</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="20"/>
+      <c r="D6" s="16">
         <v>20</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="13">
+      <c r="E6" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="19">
         <f>$F$4*D6/100</f>
         <v>0.18</v>
       </c>
-    </row>
-    <row r="7" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C7" s="3"/>
-      <c r="D7" s="7">
+      <c r="G6">
+        <v>18.23</v>
+      </c>
+      <c r="H6">
+        <v>9.9700000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C7" s="20"/>
+      <c r="D7" s="22">
         <v>30</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="13">
+      <c r="E7" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="19">
         <f>$F$4*D7/100</f>
         <v>0.27</v>
       </c>
-    </row>
-    <row r="8" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C8" s="5"/>
-      <c r="D8" s="9">
+      <c r="G7">
+        <v>27.13</v>
+      </c>
+      <c r="H7">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="24"/>
+      <c r="D8" s="16">
         <v>40</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="13">
+      <c r="E8" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="19">
         <f>$F$4*D8/100</f>
         <v>0.36</v>
       </c>
-    </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="G8">
+        <v>35.78</v>
+      </c>
+      <c r="H8">
+        <v>9.9499999999999993</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
       <c r="F9" s="15"/>
     </row>
-    <row r="10" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F10">
         <f>1-C11/100</f>
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C11" s="9">
+    <row r="11" spans="3:8" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C11" s="16">
         <v>30</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="17">
         <v>10</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="13">
+      <c r="E11" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="19">
         <f>$F$10*D11/100</f>
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="12" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C12" s="3"/>
-      <c r="D12" s="9">
+      <c r="G11">
+        <v>6.98</v>
+      </c>
+      <c r="H11">
+        <v>29.72</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C12" s="20"/>
+      <c r="D12" s="16">
         <v>20</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="13">
+      <c r="E12" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="19">
         <f>$F$10*D12/100</f>
         <v>0.14000000000000001</v>
       </c>
-    </row>
-    <row r="13" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C13" s="3"/>
-      <c r="D13" s="7">
+      <c r="G12">
+        <v>14.24</v>
+      </c>
+      <c r="H12">
+        <v>30.03</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="20"/>
+      <c r="D13" s="22">
         <v>30</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="13">
+      <c r="E13" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="19">
         <f>$F$10*D13/100</f>
         <v>0.21</v>
       </c>
-    </row>
-    <row r="14" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C14" s="5"/>
-      <c r="D14" s="9">
+      <c r="G13">
+        <v>21.37</v>
+      </c>
+      <c r="H13">
+        <v>30.37</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C14" s="24"/>
+      <c r="D14" s="16">
         <v>40</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="13">
+      <c r="E14" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="19">
         <f>$F$10*D14/100</f>
         <v>0.28000000000000003</v>
       </c>
-    </row>
-    <row r="16" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G14">
+        <v>28.25</v>
+      </c>
+      <c r="H14">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F16">
         <f>1-C17/100</f>
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C17" s="9">
+    <row r="17" spans="3:8" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="16">
         <v>50</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="17">
         <v>10</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="13">
+      <c r="E17" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="19">
         <f>$F$16*D17/100</f>
         <v>0.05</v>
       </c>
-    </row>
-    <row r="18" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C18" s="3"/>
-      <c r="D18" s="9">
+      <c r="G17" s="26">
+        <v>4.97</v>
+      </c>
+      <c r="H17" s="26">
+        <v>50.01</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C18" s="20"/>
+      <c r="D18" s="16">
         <v>20</v>
       </c>
-      <c r="E18" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" s="13">
+      <c r="E18" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="19">
         <f>$F$16*D18/100</f>
         <v>0.1</v>
       </c>
-    </row>
-    <row r="19" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C19" s="3"/>
-      <c r="D19" s="7">
+      <c r="G18" s="26">
+        <v>9.93</v>
+      </c>
+      <c r="H18" s="26">
+        <v>49.86</v>
+      </c>
+    </row>
+    <row r="19" spans="3:8" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C19" s="20"/>
+      <c r="D19" s="22">
         <v>30</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" s="13">
+      <c r="E19" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="19">
         <f>$F$16*D19/100</f>
         <v>0.15</v>
       </c>
-    </row>
-    <row r="20" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C20" s="5"/>
-      <c r="D20" s="9">
+      <c r="G19" s="26">
+        <v>14.96</v>
+      </c>
+      <c r="H19" s="26">
+        <v>49.92</v>
+      </c>
+    </row>
+    <row r="20" spans="3:8" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C20" s="24"/>
+      <c r="D20" s="16">
         <v>40</v>
       </c>
-      <c r="E20" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="13">
+      <c r="E20" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="19">
         <f>$F$16*D20/100</f>
         <v>0.2</v>
       </c>
-    </row>
-    <row r="22" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G20" s="26">
+        <v>19.96</v>
+      </c>
+      <c r="H20" s="26">
+        <v>49.44</v>
+      </c>
+    </row>
+    <row r="22" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F22">
         <f>1-C23/100</f>
         <v>0.30000000000000004</v>
       </c>
     </row>
-    <row r="23" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C23" s="9">
+    <row r="23" spans="3:8" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C23" s="16">
         <v>70</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="17">
         <v>10</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="13">
+      <c r="E23" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="19">
         <f>$F$22*D23/100</f>
         <v>3.0000000000000006E-2</v>
       </c>
-    </row>
-    <row r="24" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G23" s="27">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="H23">
+        <v>70.03</v>
+      </c>
+    </row>
+    <row r="24" spans="3:8" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C24" s="3"/>
-      <c r="D24" s="9">
+      <c r="D24" s="16">
         <v>20</v>
       </c>
-      <c r="E24" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" s="13">
+      <c r="E24" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="19">
         <f>$F$22*D24/100</f>
         <v>6.0000000000000012E-2</v>
       </c>
-    </row>
-    <row r="25" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G24" s="27">
+        <v>0.06</v>
+      </c>
+      <c r="H24">
+        <v>69.680000000000007</v>
+      </c>
+    </row>
+    <row r="25" spans="3:8" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C25" s="3"/>
-      <c r="D25" s="7">
+      <c r="D25" s="22">
         <v>30</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="13">
+      <c r="E25" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="19">
         <f>$F$22*D25/100</f>
         <v>9.0000000000000024E-2</v>
       </c>
-    </row>
-    <row r="26" spans="3:6" ht="73.3" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G25" s="27">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="H25">
+        <v>69.930000000000007</v>
+      </c>
+    </row>
+    <row r="26" spans="3:8" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C26" s="5"/>
-      <c r="D26" s="9">
+      <c r="D26" s="16">
         <v>40</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="19">
         <f>$F$22*D26/100</f>
         <v>0.12000000000000002</v>
+      </c>
+      <c r="G26" s="27">
+        <v>0.1196</v>
+      </c>
+      <c r="H26">
+        <v>70.25</v>
       </c>
     </row>
   </sheetData>
